--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.44078579686776</v>
+        <v>5.596627691991011</v>
       </c>
       <c r="D2" t="n">
-        <v>34.373504043373</v>
+        <v>5.585694407048114</v>
       </c>
       <c r="E2" t="n">
-        <v>4.573254255080155</v>
+        <v>0.7431538164505251</v>
       </c>
       <c r="F2" t="n">
-        <v>4.627073232574025</v>
+        <v>0.7518994002932791</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.61868958220526</v>
+        <v>6.438037057108354</v>
       </c>
       <c r="D3" t="n">
-        <v>39.77380085901434</v>
+        <v>6.46324263958983</v>
       </c>
       <c r="E3" t="n">
-        <v>4.573254255080155</v>
+        <v>0.7431538164505251</v>
       </c>
       <c r="F3" t="n">
-        <v>4.627073232574025</v>
+        <v>0.7518994002932791</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.34401161020045</v>
+        <v>5.905901886657574</v>
       </c>
       <c r="D4" t="n">
-        <v>36.71590043843217</v>
+        <v>5.966333821245228</v>
       </c>
       <c r="E4" t="n">
-        <v>4.573254255080155</v>
+        <v>0.7431538164505251</v>
       </c>
       <c r="F4" t="n">
-        <v>4.627073232574025</v>
+        <v>0.7518994002932791</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.6163454697523</v>
+        <v>4.975156138834749</v>
       </c>
       <c r="D5" t="n">
-        <v>30.24751901888466</v>
+        <v>4.915221840568758</v>
       </c>
       <c r="E5" t="n">
-        <v>4.573254255080155</v>
+        <v>0.7431538164505251</v>
       </c>
       <c r="F5" t="n">
-        <v>4.627073232574025</v>
+        <v>0.7518994002932791</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.35405442672771</v>
+        <v>5.745033844343252</v>
       </c>
       <c r="D6" t="n">
-        <v>35.71861909369611</v>
+        <v>5.804275602725618</v>
       </c>
       <c r="E6" t="n">
-        <v>4.573254255080155</v>
+        <v>0.7431538164505251</v>
       </c>
       <c r="F6" t="n">
-        <v>4.627073232574025</v>
+        <v>0.7518994002932791</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.29045303404975</v>
+        <v>4.109698618033085</v>
       </c>
       <c r="D7" t="n">
-        <v>25.57405590605907</v>
+        <v>4.155784084734599</v>
       </c>
       <c r="E7" t="n">
-        <v>4.573254255080155</v>
+        <v>0.7431538164505251</v>
       </c>
       <c r="F7" t="n">
-        <v>4.627073232574025</v>
+        <v>0.7518994002932791</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
